--- a/utils/Consolidated_WP_Template.xlsx
+++ b/utils/Consolidated_WP_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/52580622446e5424/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Subho syste,\ControlTester_3000_kv\utils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{08648CC8-8C50-4E3E-B315-03E7BC9947FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99708E07-68A7-43C1-9F02-3BC097A14862}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF709686-0244-42BF-834E-C7F74FB2ADEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{58917B3C-72A9-4D9B-BA04-995DFB074748}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{58917B3C-72A9-4D9B-BA04-995DFB074748}"/>
   </bookViews>
   <sheets>
     <sheet name="ICMP" sheetId="1" r:id="rId1"/>
@@ -332,7 +332,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -342,33 +342,64 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFA6A6A6"/>
       </left>
       <right style="thin">
         <color rgb="FFA6A6A6"/>
       </right>
-      <top style="thin">
-        <color rgb="FFA6A6A6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA6A6A6"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -376,24 +407,122 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -411,6 +540,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Instructions"/>
@@ -442,11 +572,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E44E7924-69FD-4DCC-8764-384ED0DA40AE}" name="PriorIssues" displayName="PriorIssues" ref="A63:E73">
   <autoFilter ref="A63:E73" xr:uid="{E44E7924-69FD-4DCC-8764-384ED0DA40AE}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{93920E78-9DAF-4807-B75D-8D2612230DD9}" name="Issue ID"/>
-    <tableColumn id="2" xr3:uid="{B528DC0F-B4C5-48EB-B361-221CF2E29117}" name="Issue description"/>
-    <tableColumn id="3" xr3:uid="{3C3D9F8A-548F-4581-9774-8B4519B6D928}" name="Status"/>
-    <tableColumn id="4" xr3:uid="{388B4A21-0091-4443-A327-81E52BF118A6}" name="Reference"/>
-    <tableColumn id="5" xr3:uid="{4A7A9F51-51F8-47B7-9F2F-2BBCD7E28F81}" name="Notes"/>
+    <tableColumn id="1" xr3:uid="{93920E78-9DAF-4807-B75D-8D2612230DD9}" name="Issue ID" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{B528DC0F-B4C5-48EB-B361-221CF2E29117}" name="Issue description" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{3C3D9F8A-548F-4581-9774-8B4519B6D928}" name="Status" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{388B4A21-0091-4443-A327-81E52BF118A6}" name="Reference" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{4A7A9F51-51F8-47B7-9F2F-2BBCD7E28F81}" name="Notes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -770,921 +900,960 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34E84636-740F-4609-BFD6-700EF04CC6C3}">
   <dimension ref="A1:H87"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="71.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.77734375" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-    </row>
-    <row r="3" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="6"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="6"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <f>[1]WP_Summary!B4</f>
         <v>0</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="6"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="23" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="23" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-    </row>
-    <row r="25" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B25" s="6"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-    </row>
-    <row r="26" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B26" s="6"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-    </row>
-    <row r="27" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B27" s="6"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-    </row>
-    <row r="28" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B28" s="6"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B29" s="6"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-    </row>
-    <row r="31" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="31" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-    </row>
-    <row r="32" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+    </row>
+    <row r="32" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-    </row>
-    <row r="33" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B33" s="6"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-    </row>
-    <row r="34" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B34" s="6"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-    </row>
-    <row r="35" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B35" s="6"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-    </row>
-    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="37" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-    </row>
-    <row r="38" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B38" s="6"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-    </row>
-    <row r="39" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B39" s="6"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-    </row>
-    <row r="40" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B40" s="6"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-    </row>
-    <row r="41" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+    </row>
+    <row r="41" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B41" s="6"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-    </row>
-    <row r="42" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="1" t="s">
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B42" s="6"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-    </row>
-    <row r="43" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="1" t="s">
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+    </row>
+    <row r="43" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B43" s="6"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-    </row>
-    <row r="44" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+    </row>
+    <row r="44" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B44" s="6"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-    </row>
-    <row r="45" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+    </row>
+    <row r="45" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B45" s="6"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-    </row>
-    <row r="46" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B46" s="6"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-    </row>
-    <row r="47" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="1" t="s">
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+    </row>
+    <row r="47" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B47" s="6"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-    </row>
-    <row r="48" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+    </row>
+    <row r="48" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B48" s="6"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-    </row>
-    <row r="49" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+    </row>
+    <row r="49" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B49" s="6"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-    </row>
-    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="51" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-    </row>
-    <row r="52" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="1" t="s">
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+    </row>
+    <row r="52" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="5" t="s">
         <v>46</v>
       </c>
       <c r="B52" s="6"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-    </row>
-    <row r="53" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+    </row>
+    <row r="53" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B53" s="6"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-    </row>
-    <row r="54" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B54" s="6"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-    </row>
-    <row r="55" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+    </row>
+    <row r="55" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B55" s="6"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-    </row>
-    <row r="56" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="1" t="s">
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+    </row>
+    <row r="56" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B56" s="6"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-    </row>
-    <row r="57" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="1" t="s">
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+    </row>
+    <row r="57" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B57" s="6"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-    </row>
-    <row r="58" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="1" t="s">
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B58" s="6"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-    </row>
-    <row r="59" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="1" t="s">
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+    </row>
+    <row r="59" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B59" s="6"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="7"/>
-    </row>
-    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+    </row>
+    <row r="62" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="7"/>
-      <c r="H62" s="7"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A63" s="4" t="s">
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="11" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-    </row>
-    <row r="76" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="9" t="s">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="10"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="10"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="10"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="10"/>
+      <c r="B67" s="10"/>
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="10"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="10"/>
+      <c r="B69" s="10"/>
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="10"/>
+      <c r="B70" s="10"/>
+      <c r="C70" s="10"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="10"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="10"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="10"/>
+      <c r="B72" s="10"/>
+      <c r="C72" s="10"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="10"/>
+      <c r="B73" s="10"/>
+      <c r="C73" s="10"/>
+      <c r="D73" s="10"/>
+      <c r="E73" s="10"/>
+    </row>
+    <row r="76" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="7"/>
-      <c r="H76" s="7"/>
-    </row>
-    <row r="77" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="3" t="s">
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+    </row>
+    <row r="77" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B77" s="10">
+      <c r="B77" s="9">
         <f>[1]WP_Summary!B65</f>
         <v>0</v>
       </c>
-      <c r="C77" s="7"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="7"/>
-      <c r="G77" s="7"/>
-      <c r="H77" s="7"/>
-    </row>
-    <row r="78" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="8" t="s">
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="7"/>
-      <c r="G78" s="7"/>
-      <c r="H78" s="7"/>
-    </row>
-    <row r="79" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="1" t="s">
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="5" t="s">
         <v>61</v>
       </c>
       <c r="B79" s="6"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-    </row>
-    <row r="80" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="1" t="s">
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="5" t="s">
         <v>62</v>
       </c>
       <c r="B80" s="6"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-    </row>
-    <row r="81" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="1" t="s">
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4"/>
+    </row>
+    <row r="81" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B81" s="6"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="7"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-    </row>
-    <row r="82" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="1" t="s">
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B82" s="6"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="7"/>
-      <c r="H82" s="7"/>
-    </row>
-    <row r="84" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="8" t="s">
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+    </row>
+    <row r="84" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
-    </row>
-    <row r="85" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="4" t="s">
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+    </row>
+    <row r="85" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E85" s="4" t="s">
+      <c r="E85" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="F85" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="G85" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="H85" s="4" t="s">
+      <c r="H85" s="12" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="5"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-    </row>
-    <row r="87" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="5"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
+    <row r="86" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="13"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="10"/>
+      <c r="D86" s="10"/>
+      <c r="E86" s="10"/>
+      <c r="F86" s="10"/>
+      <c r="G86" s="10"/>
+      <c r="H86" s="10"/>
+    </row>
+    <row r="87" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="13"/>
+      <c r="B87" s="10"/>
+      <c r="C87" s="10"/>
+      <c r="D87" s="10"/>
+      <c r="E87" s="10"/>
+      <c r="F87" s="10"/>
+      <c r="G87" s="10"/>
+      <c r="H87" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="63">
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B81:H81"/>
+    <mergeCell ref="B82:H82"/>
+    <mergeCell ref="A84:H84"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="B77:H77"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="B79:H79"/>
+    <mergeCell ref="B80:H80"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B32:H32"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B9:H9"/>
@@ -1697,51 +1866,12 @@
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="B25:H25"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B28:H28"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="B44:H44"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="B47:H47"/>
-    <mergeCell ref="B48:H48"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B53:H53"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B56:H56"/>
-    <mergeCell ref="B57:H57"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B81:H81"/>
-    <mergeCell ref="B82:H82"/>
-    <mergeCell ref="A84:H84"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A76:H76"/>
-    <mergeCell ref="B77:H77"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="B79:H79"/>
-    <mergeCell ref="B80:H80"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B6:H6"/>
   </mergeCells>
   <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" sqref="B24" xr:uid="{B4076DF8-C2E2-45D9-BD7F-43B8DDA2C246}">
